--- a/JobIntel/sql/query_results/skill_demand_by_category.xlsx
+++ b/JobIntel/sql/query_results/skill_demand_by_category.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42a4dbeb8f84b5af/Desktop/AI-Powered-Job-Market-Intelligence-Platform/AI-Powered-Job-Market-Intelligence-Platform/JobIntel/sql/query_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A438DA03-0EED-4CC9-BB37-8C436FBE71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{A438DA03-0EED-4CC9-BB37-8C436FBE71EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{244EE1B0-FB12-489E-B3B7-CFC60ED09A6A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{46F65A69-0BF9-46F7-9F90-F245496E427F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Business</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>AI</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>demand</t>
   </si>
 </sst>
 </file>
@@ -424,71 +430,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BB0D17-9511-4E44-93D8-98B7AEB65666}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>107107</v>
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>20490</v>
+        <v>106469</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>15517</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>11455</v>
+        <v>15429</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>9339</v>
+        <v>11364</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>9245</v>
+        <v>9290</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>7486</v>
+        <v>9195</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>6761</v>
+        <v>7459</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -496,23 +502,23 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>4913</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>2421</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>1679</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,15 +526,23 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1667</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>1114</v>
+      <c r="B14">
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
